--- a/themes/arrest.xlsx
+++ b/themes/arrest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,139 +450,79 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Адреса и режим работы офисов банка вы найдете в [этом разделе]({{$temp.officeLink}})</t>
+          <t xml:space="preserve">    • Ограничено время приема средств на счет до 18:00 по мск с пн по пт</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Адреса и режим работы офисов банка вы найдете в [этом разделе]({{$temp.officeLink}}).</t>
+          <t xml:space="preserve">    • Ограничено время приема средств на счет до 18:00 по МСК с пн по пт</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>«мск» приведено к «МСК» — для единообразия с соседним пунктом (стр. 47), где аббревиатура пишется заглавными</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • Ограничено время приема средств на счет до 18:00 по мск с пн по пт</t>
+          <t xml:space="preserve">    - Арест со счета снимается в течение 7 -10 рабочих дней с момента поступления в банк документов о снятии.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    • Ограничено время приема средств на счет до 18:00 по МСК с пн по пт</t>
+          <t xml:space="preserve">    - Арест со счета снимается в течение 7–10 рабочих дней с момента поступления в банк документов о снятии.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>«мск» приведено к «МСК» — для единообразия с соседним пунктом (стр. 47), где аббревиатура пишется заглавными</t>
+          <t>убран лишний пробел, дефис заменён на короткое тире для диапазона чисел</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Проверить налоговый арест можно при личном обращении в ФНС или в [личном кабинете налогоплательщика](https://lkfl2.nalog.ru/lkfl)</t>
+          <t xml:space="preserve">    - Чтобы уточнить детали напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или в [веб-версии на сайте](https://online.uralsib.ru)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Проверить налоговый арест можно при личном обращении в ФНС или в [личном кабинете налогоплательщика](https://lkfl2.nalog.ru/lkfl).</t>
+          <t xml:space="preserve">    - Чтобы уточнить детали, напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или в [веб-версии на сайте](https://online.uralsib.ru)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>добавлена запятая после придаточного «Чтобы уточнить детали»</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - Посмотреть информацию по действующим арестам можно на официальном [сайте ФССП](https://fssp.gov.ru/iss/ip)</t>
+          <t xml:space="preserve">  Reply: Арест со счета снимается в течение 7 -10 рабочих дней с момента поступления в банк документов о снятии.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - Посмотреть информацию по действующим арестам можно на официальном [сайте ФССП](https://fssp.gov.ru/iss/ip).</t>
+          <t xml:space="preserve">  Reply: Арест со счета снимается в течение 7–10 рабочих дней с момента поступления в банк документов о снятии.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>92</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Арест со счета снимается в течение 7 -10 рабочих дней с момента поступления в банк документов о снятии.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Арест со счета снимается в течение 7–10 рабочих дней с момента поступления в банк документов о снятии.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>убран лишний пробел, дефис заменён на короткое тире для диапазона чисел</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>93</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Чтобы уточнить детали напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или в [веб-версии на сайте](https://online.uralsib.ru)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    - Чтобы уточнить детали, напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или в [веб-версии на сайте](https://online.uralsib.ru).</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>добавлена запятая после придаточного «Чтобы уточнить детали»; добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>94</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Reply: Арест со счета снимается в течение 7 -10 рабочих дней с момента поступления в банк документов о снятии.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Reply: Арест со счета снимается в течение 7–10 рабочих дней с момента поступления в банк документов о снятии.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
         <is>
           <t>убран лишний пробел, дефис заменён на короткое тире для диапазона чисел</t>
         </is>
